--- a/xls/square_16_quad4_20.xlsx
+++ b/xls/square_16_quad4_20.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18">
+        <v>441</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18">
+        <v>289</v>
+      </c>
+      <c r="E18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18">
+        <v>361</v>
+      </c>
+      <c r="G18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18">
+        <v>972</v>
+      </c>
+      <c r="I18">
+        <v>-0.18497122130611027</v>
+      </c>
+      <c r="J18">
+        <v>-1.1616478496680085</v>
+      </c>
+      <c r="K18">
+        <v>1.5721008631680051</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19">
+        <v>441</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19">
+        <v>289</v>
+      </c>
+      <c r="E19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19">
+        <v>400</v>
+      </c>
+      <c r="G19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19">
+        <v>1083</v>
+      </c>
+      <c r="I19">
+        <v>-1.0972030698684787</v>
+      </c>
+      <c r="J19">
+        <v>-1.4952411321728558</v>
+      </c>
+      <c r="K19">
+        <v>1.4475066379412898</v>
+      </c>
+    </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
         <v>11</v>
@@ -482,13 +552,13 @@
         <v>1200</v>
       </c>
       <c r="I20">
-        <v>0.45775675550053263</v>
+        <v>-1.2637755523635597</v>
       </c>
       <c r="J20">
-        <v>-1.889708117674421</v>
+        <v>-1.5630262348007464</v>
       </c>
       <c r="K20">
-        <v>1.8176062075987798</v>
+        <v>1.7364335647023024</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -517,13 +587,13 @@
         <v>1323</v>
       </c>
       <c r="I21">
-        <v>-1.8380026008860786</v>
+        <v>-1.294821691514661</v>
       </c>
       <c r="J21">
-        <v>-1.81387623846648</v>
+        <v>-1.3948450521755085</v>
       </c>
       <c r="K21">
-        <v>1.1513090176879583</v>
+        <v>3.021028889895441</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -552,13 +622,13 @@
         <v>1452</v>
       </c>
       <c r="I22">
-        <v>-1.731005662598277</v>
+        <v>-1.3248741846288241</v>
       </c>
       <c r="J22">
-        <v>-1.7083575943615767</v>
+        <v>-1.2976885388563728</v>
       </c>
       <c r="K22">
-        <v>1.9103098231630584</v>
+        <v>4.416855527721151</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -587,13 +657,13 @@
         <v>1587</v>
       </c>
       <c r="I23">
-        <v>-1.6104178485522602</v>
+        <v>-1.098702428336827</v>
       </c>
       <c r="J23">
-        <v>-1.5939835598873149</v>
+        <v>-0.9402623787919161</v>
       </c>
       <c r="K23">
-        <v>2.3180677605217035</v>
+        <v>4.737335913649453</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -622,13 +692,13 @@
         <v>1728</v>
       </c>
       <c r="I24">
-        <v>-1.339307515297343</v>
+        <v>-0.2675260000390515</v>
       </c>
       <c r="J24">
-        <v>-0.9156545069089413</v>
+        <v>-0.24307267543582026</v>
       </c>
       <c r="K24">
-        <v>2.753828275595455</v>
+        <v>4.8782322405117355</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -657,13 +727,13 @@
         <v>1875</v>
       </c>
       <c r="I25">
-        <v>-0.715865486368775</v>
+        <v>-0.004637849211737409</v>
       </c>
       <c r="J25">
-        <v>-0.49097967828370676</v>
+        <v>-0.0041325468032509406</v>
       </c>
       <c r="K25">
-        <v>3.7810842432214145</v>
+        <v>4.191131633248962</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -692,13 +762,13 @@
         <v>2028</v>
       </c>
       <c r="I26">
-        <v>-0.11040267078773479</v>
+        <v>-0.0011972780716210099</v>
       </c>
       <c r="J26">
-        <v>-0.10188724413130655</v>
+        <v>-0.0011239366033355552</v>
       </c>
       <c r="K26">
-        <v>3.7676791210209166</v>
+        <v>3.942915625119496</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -727,13 +797,13 @@
         <v>2187</v>
       </c>
       <c r="I27">
-        <v>-0.0050631681950504175</v>
+        <v>-3.599274398990075e-5</v>
       </c>
       <c r="J27">
-        <v>-0.004735228828270463</v>
+        <v>-3.368000772193974e-5</v>
       </c>
       <c r="K27">
-        <v>3.2715006080705566</v>
+        <v>3.171761627764352</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -762,13 +832,13 @@
         <v>2352</v>
       </c>
       <c r="I28">
-        <v>-0.00016461951902849552</v>
+        <v>-4.039501325482697e-6</v>
       </c>
       <c r="J28">
-        <v>-0.00019063100048865808</v>
+        <v>-4.029065636249553e-6</v>
       </c>
       <c r="K28">
-        <v>2.6406282459002735</v>
+        <v>2.7425846250993176</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -797,13 +867,13 @@
         <v>2523</v>
       </c>
       <c r="I29">
-        <v>-0.0011012638725614078</v>
+        <v>-1.2265750906474664e-5</v>
       </c>
       <c r="J29">
-        <v>-0.0011055018922543887</v>
+        <v>-1.2496240827800295e-5</v>
       </c>
       <c r="K29">
-        <v>2.9840958918362626</v>
+        <v>2.983073256938686</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -832,13 +902,13 @@
         <v>2700</v>
       </c>
       <c r="I30">
-        <v>-0.000714821996400893</v>
+        <v>-5.031957465152408e-6</v>
       </c>
       <c r="J30">
-        <v>-0.0007214380846049131</v>
+        <v>-5.016753385589871e-6</v>
       </c>
       <c r="K30">
-        <v>2.910824800004739</v>
+        <v>2.7668740037604507</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -867,13 +937,13 @@
         <v>2883</v>
       </c>
       <c r="I31">
-        <v>-0.00022350609759874096</v>
+        <v>-2.4942618965867866e-6</v>
       </c>
       <c r="J31">
-        <v>-0.00023476685961259158</v>
+        <v>-2.5506806636085994e-6</v>
       </c>
       <c r="K31">
-        <v>2.7005678160618367</v>
+        <v>2.658957587882427</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -902,13 +972,13 @@
         <v>3072</v>
       </c>
       <c r="I32">
-        <v>-0.00028743793580563175</v>
+        <v>-2.734432881582039e-6</v>
       </c>
       <c r="J32">
-        <v>-0.00031229335288838117</v>
+        <v>-2.8406592045150735e-6</v>
       </c>
       <c r="K32">
-        <v>2.7433112156720547</v>
+        <v>2.667295918461444</v>
       </c>
     </row>
   </sheetData>
